--- a/data/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ48"/>
+  <dimension ref="A1:AJ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6158,8 +6158,1704 @@
       <c r="AI48" s="2" t="inlineStr"/>
       <c r="AJ48" s="2" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ff4c023688d14058</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>69680</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0.653037</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0.043662</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:25.435587Z</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=ff4c023688d14058;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>add1d14a4c2b420d</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>69681</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>0.616374</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.669967</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>-0.053593</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:25.920075Z</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=add1d14a4c2b420d;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
+      <c r="AJ50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>a975d9cc6cd1438a</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>69682</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>0.684497</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0.629630</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>0.054867</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:26.448910Z</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=a975d9cc6cd1438a;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>b1eff2d834ee4531</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>69289</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>0.510880</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0.420168</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>0.090712</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:27.457693Z</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=b1eff2d834ee4531;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr"/>
+      <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AG52" s="2" t="inlineStr"/>
+      <c r="AH52" s="2" t="inlineStr"/>
+      <c r="AI52" s="2" t="inlineStr"/>
+      <c r="AJ52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>4cc088e9a58a432c</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>0.579723</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>0.440529</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>0.139194</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:27.987395Z</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=4cc088e9a58a432c;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr"/>
+      <c r="AE53" s="2" t="inlineStr"/>
+      <c r="AF53" s="2" t="inlineStr"/>
+      <c r="AG53" s="2" t="inlineStr"/>
+      <c r="AH53" s="2" t="inlineStr"/>
+      <c r="AI53" s="2" t="inlineStr"/>
+      <c r="AJ53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>dcd060b9a66d4474</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>67577</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>0.527028</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>-0.082347</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:28.508356Z</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=dcd060b9a66d4474;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr"/>
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="2" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>8b565a880bc641fd</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>68288</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>0.704469</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>0.313844</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:29.628121Z</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=8b565a880bc641fd;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr"/>
+      <c r="AE55" s="2" t="inlineStr"/>
+      <c r="AF55" s="2" t="inlineStr"/>
+      <c r="AG55" s="2" t="inlineStr"/>
+      <c r="AH55" s="2" t="inlineStr"/>
+      <c r="AI55" s="2" t="inlineStr"/>
+      <c r="AJ55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>29fd0577e0e047f2</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>67510</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0.563160</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0.690402</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>-0.127242</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:31.160500Z</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=29fd0577e0e047f2;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr"/>
+      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
+      <c r="AG56" s="2" t="inlineStr"/>
+      <c r="AH56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr"/>
+      <c r="AJ56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>0cc692592b584103</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>0.599394</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>0.579832</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>0.019562</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:31.676274Z</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=0cc692592b584103;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr"/>
+      <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AG57" s="2" t="inlineStr"/>
+      <c r="AH57" s="2" t="inlineStr"/>
+      <c r="AI57" s="2" t="inlineStr"/>
+      <c r="AJ57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>b4129a3a513c483d</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>69267</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>0.629130</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>0.680511</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>-0.051381</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:34.287196Z</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=b4129a3a513c483d;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
+      <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AG58" s="2" t="inlineStr"/>
+      <c r="AH58" s="2" t="inlineStr"/>
+      <c r="AI58" s="2" t="inlineStr"/>
+      <c r="AJ58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>28dc3f7209da4b8c</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>69135</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>0.527344</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>0.619772</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>-0.092428</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:34.811836Z</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=28dc3f7209da4b8c;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr"/>
+      <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AF59" s="2" t="inlineStr"/>
+      <c r="AG59" s="2" t="inlineStr"/>
+      <c r="AH59" s="2" t="inlineStr"/>
+      <c r="AI59" s="2" t="inlineStr"/>
+      <c r="AJ59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>e4e741f10bd84db0</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>67578</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>0.527028</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0.600000</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>-0.072972</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:35.357223Z</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=e4e741f10bd84db0;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr"/>
+      <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AF60" s="2" t="inlineStr"/>
+      <c r="AG60" s="2" t="inlineStr"/>
+      <c r="AH60" s="2" t="inlineStr"/>
+      <c r="AI60" s="2" t="inlineStr"/>
+      <c r="AJ60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>f4969aeb2da94d49</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>67579</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>0.526276</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>0.340136</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>0.186140</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:35.908816Z</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=f4969aeb2da94d49;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr"/>
+      <c r="AE61" s="2" t="inlineStr"/>
+      <c r="AF61" s="2" t="inlineStr"/>
+      <c r="AG61" s="2" t="inlineStr"/>
+      <c r="AH61" s="2" t="inlineStr"/>
+      <c r="AI61" s="2" t="inlineStr"/>
+      <c r="AJ61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>1cffdca8c7bc4808</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>68292</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>0.614071</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>0.650350</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>-0.036279</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:36.873973Z</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=1cffdca8c7bc4808;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr"/>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr"/>
+      <c r="AE62" s="2" t="inlineStr"/>
+      <c r="AF62" s="2" t="inlineStr"/>
+      <c r="AG62" s="2" t="inlineStr"/>
+      <c r="AH62" s="2" t="inlineStr"/>
+      <c r="AI62" s="2" t="inlineStr"/>
+      <c r="AJ62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>9369df9452e344ef</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>0.681973</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>0.640288</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>0.041685</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:37.423413Z</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=9369df9452e344ef;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr"/>
+      <c r="AE63" s="2" t="inlineStr"/>
+      <c r="AF63" s="2" t="inlineStr"/>
+      <c r="AG63" s="2" t="inlineStr"/>
+      <c r="AH63" s="2" t="inlineStr"/>
+      <c r="AI63" s="2" t="inlineStr"/>
+      <c r="AJ63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>495eaed7b34a4c93</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>0.569799</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>0.450450</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>0.119349</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:41.320292Z</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/cs2.xlsx;original_pick_id=495eaed7b34a4c93;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr"/>
+      <c r="AE64" s="2" t="inlineStr"/>
+      <c r="AF64" s="2" t="inlineStr"/>
+      <c r="AG64" s="2" t="inlineStr"/>
+      <c r="AH64" s="2" t="inlineStr"/>
+      <c r="AI64" s="2" t="inlineStr"/>
+      <c r="AJ64" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ48"/>
+  <autoFilter ref="A1:AJ64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ64"/>
+  <dimension ref="A1:AJ77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7854,8 +7854,1334 @@
       <c r="AI64" s="2" t="inlineStr"/>
       <c r="AJ64" s="2" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>b120db594a3b4614</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>0.579552</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>0.1390233656387665</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:43.326707Z</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr"/>
+      <c r="AE65" s="2" t="inlineStr"/>
+      <c r="AF65" s="2" t="inlineStr"/>
+      <c r="AG65" s="2" t="inlineStr"/>
+      <c r="AH65" s="2" t="inlineStr"/>
+      <c r="AI65" s="2" t="inlineStr"/>
+      <c r="AJ65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>73e0359948374332</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>67577</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>0.526938</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>-0.08243699999999998</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:43.920209Z</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="2" t="inlineStr"/>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr"/>
+      <c r="AE66" s="2" t="inlineStr"/>
+      <c r="AF66" s="2" t="inlineStr"/>
+      <c r="AG66" s="2" t="inlineStr"/>
+      <c r="AH66" s="2" t="inlineStr"/>
+      <c r="AI66" s="2" t="inlineStr"/>
+      <c r="AJ66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>68968455028c4a22</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>0.599199</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>0.019367067226890855</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:46.352076Z</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr"/>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr"/>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr"/>
+      <c r="AE67" s="2" t="inlineStr"/>
+      <c r="AF67" s="2" t="inlineStr"/>
+      <c r="AG67" s="2" t="inlineStr"/>
+      <c r="AH67" s="2" t="inlineStr"/>
+      <c r="AI67" s="2" t="inlineStr"/>
+      <c r="AJ67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2322d797bc3b4ce7</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>67510</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>0.563071</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>-0.12733147678018575</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:47.796652Z</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr"/>
+      <c r="W68" s="2" t="inlineStr"/>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" s="2" t="inlineStr"/>
+      <c r="AA68" s="2" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr"/>
+      <c r="AE68" s="2" t="inlineStr"/>
+      <c r="AF68" s="2" t="inlineStr"/>
+      <c r="AG68" s="2" t="inlineStr"/>
+      <c r="AH68" s="2" t="inlineStr"/>
+      <c r="AI68" s="2" t="inlineStr"/>
+      <c r="AJ68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>0ba2edc0355849fc</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>67514</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>0.639896</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>0.02012413688212933</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:48.789246Z</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr"/>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr"/>
+      <c r="AA69" s="2" t="inlineStr"/>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr"/>
+      <c r="AE69" s="2" t="inlineStr"/>
+      <c r="AF69" s="2" t="inlineStr"/>
+      <c r="AG69" s="2" t="inlineStr"/>
+      <c r="AH69" s="2" t="inlineStr"/>
+      <c r="AI69" s="2" t="inlineStr"/>
+      <c r="AJ69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>50e39d12dba945e6</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>69135</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>0.527201</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>-0.09257086311787066</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:49.284497Z</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr"/>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr"/>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr"/>
+      <c r="AE70" s="2" t="inlineStr"/>
+      <c r="AF70" s="2" t="inlineStr"/>
+      <c r="AG70" s="2" t="inlineStr"/>
+      <c r="AH70" s="2" t="inlineStr"/>
+      <c r="AI70" s="2" t="inlineStr"/>
+      <c r="AJ70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>b86e6feff07840a3</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>69267</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>0.628836</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>-0.051675182108626205</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:49.833473Z</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr"/>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr"/>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr"/>
+      <c r="AE71" s="2" t="inlineStr"/>
+      <c r="AF71" s="2" t="inlineStr"/>
+      <c r="AG71" s="2" t="inlineStr"/>
+      <c r="AH71" s="2" t="inlineStr"/>
+      <c r="AI71" s="2" t="inlineStr"/>
+      <c r="AJ71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>5a74ebd5b033430c</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>67578</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>0.526938</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>-0.07306200000000007</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:50.485383Z</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr"/>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr"/>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr"/>
+      <c r="AE72" s="2" t="inlineStr"/>
+      <c r="AF72" s="2" t="inlineStr"/>
+      <c r="AG72" s="2" t="inlineStr"/>
+      <c r="AH72" s="2" t="inlineStr"/>
+      <c r="AI72" s="2" t="inlineStr"/>
+      <c r="AJ72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>4c113866808e4219</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>67579</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>0.526281</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>0.1861449455782313</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:50.962336Z</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr"/>
+      <c r="W73" s="2" t="inlineStr"/>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr"/>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr"/>
+      <c r="AE73" s="2" t="inlineStr"/>
+      <c r="AF73" s="2" t="inlineStr"/>
+      <c r="AG73" s="2" t="inlineStr"/>
+      <c r="AH73" s="2" t="inlineStr"/>
+      <c r="AI73" s="2" t="inlineStr"/>
+      <c r="AJ73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>215d82c08cef44af</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>0.663041</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>0.022753230215827314</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:51.418739Z</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr"/>
+      <c r="W74" s="2" t="inlineStr"/>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr"/>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr"/>
+      <c r="AE74" s="2" t="inlineStr"/>
+      <c r="AF74" s="2" t="inlineStr"/>
+      <c r="AG74" s="2" t="inlineStr"/>
+      <c r="AH74" s="2" t="inlineStr"/>
+      <c r="AI74" s="2" t="inlineStr"/>
+      <c r="AJ74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>63957c45ba11484c</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>68292</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>0.613913</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>-0.026374769784172636</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:51.886373Z</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr"/>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr"/>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr"/>
+      <c r="AE75" s="2" t="inlineStr"/>
+      <c r="AF75" s="2" t="inlineStr"/>
+      <c r="AG75" s="2" t="inlineStr"/>
+      <c r="AH75" s="2" t="inlineStr"/>
+      <c r="AI75" s="2" t="inlineStr"/>
+      <c r="AJ75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>c70e40890f6343f5</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>0.569636</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>0.11918554954954952</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:55.995920Z</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr"/>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr"/>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr"/>
+      <c r="AE76" s="2" t="inlineStr"/>
+      <c r="AF76" s="2" t="inlineStr"/>
+      <c r="AG76" s="2" t="inlineStr"/>
+      <c r="AH76" s="2" t="inlineStr"/>
+      <c r="AI76" s="2" t="inlineStr"/>
+      <c r="AJ76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>0d0644464ca24e6a</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>0.57961</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>0.1390813656387665</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:36.926594Z</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr"/>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr"/>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr"/>
+      <c r="AE77" s="2" t="inlineStr"/>
+      <c r="AF77" s="2" t="inlineStr"/>
+      <c r="AG77" s="2" t="inlineStr"/>
+      <c r="AH77" s="2" t="inlineStr"/>
+      <c r="AI77" s="2" t="inlineStr"/>
+      <c r="AJ77" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ64"/>
+  <autoFilter ref="A1:AJ77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ77"/>
+  <dimension ref="A1:AJ89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -9180,8 +9180,1232 @@
       <c r="AI77" s="2" t="inlineStr"/>
       <c r="AJ77" s="2" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>b154d46ecd8e4649</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>0.57961</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>0.1390813656387665</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:31.889837Z</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr"/>
+      <c r="W78" s="2" t="inlineStr"/>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="2" t="inlineStr"/>
+      <c r="AA78" s="2" t="inlineStr"/>
+      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr"/>
+      <c r="AE78" s="2" t="inlineStr"/>
+      <c r="AF78" s="2" t="inlineStr"/>
+      <c r="AG78" s="2" t="inlineStr"/>
+      <c r="AH78" s="2" t="inlineStr"/>
+      <c r="AI78" s="2" t="inlineStr"/>
+      <c r="AJ78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>4d6be84a20f747c8</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>67577</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>0.52695</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>-0.08242499999999997</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:32.462110Z</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr"/>
+      <c r="W79" s="2" t="inlineStr"/>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="2" t="inlineStr"/>
+      <c r="AA79" s="2" t="inlineStr"/>
+      <c r="AB79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr"/>
+      <c r="AE79" s="2" t="inlineStr"/>
+      <c r="AF79" s="2" t="inlineStr"/>
+      <c r="AG79" s="2" t="inlineStr"/>
+      <c r="AH79" s="2" t="inlineStr"/>
+      <c r="AI79" s="2" t="inlineStr"/>
+      <c r="AJ79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>b04a6258eed7467d</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>0.599274</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>0.01944206722689079</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:35.118991Z</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr"/>
+      <c r="W80" s="2" t="inlineStr"/>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr"/>
+      <c r="Z80" s="2" t="inlineStr"/>
+      <c r="AA80" s="2" t="inlineStr"/>
+      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr"/>
+      <c r="AE80" s="2" t="inlineStr"/>
+      <c r="AF80" s="2" t="inlineStr"/>
+      <c r="AG80" s="2" t="inlineStr"/>
+      <c r="AH80" s="2" t="inlineStr"/>
+      <c r="AI80" s="2" t="inlineStr"/>
+      <c r="AJ80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>49b319558cad4d38</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>67510</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>0.563115</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>-0.1272874767801857</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:36.680077Z</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr"/>
+      <c r="W81" s="2" t="inlineStr"/>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr"/>
+      <c r="Z81" s="2" t="inlineStr"/>
+      <c r="AA81" s="2" t="inlineStr"/>
+      <c r="AB81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr"/>
+      <c r="AE81" s="2" t="inlineStr"/>
+      <c r="AF81" s="2" t="inlineStr"/>
+      <c r="AG81" s="2" t="inlineStr"/>
+      <c r="AH81" s="2" t="inlineStr"/>
+      <c r="AI81" s="2" t="inlineStr"/>
+      <c r="AJ81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>995f0faaf9c84a6e</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>67514</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>0.640004</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>0.020232136882129326</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:37.624827Z</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr"/>
+      <c r="W82" s="2" t="inlineStr"/>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr"/>
+      <c r="Z82" s="2" t="inlineStr"/>
+      <c r="AA82" s="2" t="inlineStr"/>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr"/>
+      <c r="AE82" s="2" t="inlineStr"/>
+      <c r="AF82" s="2" t="inlineStr"/>
+      <c r="AG82" s="2" t="inlineStr"/>
+      <c r="AH82" s="2" t="inlineStr"/>
+      <c r="AI82" s="2" t="inlineStr"/>
+      <c r="AJ82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>811f6557939043e9</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>69267</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>0.628935</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>-0.051576182108626134</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:38.106265Z</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="2" t="inlineStr"/>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr"/>
+      <c r="Z83" s="2" t="inlineStr"/>
+      <c r="AA83" s="2" t="inlineStr"/>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr"/>
+      <c r="AE83" s="2" t="inlineStr"/>
+      <c r="AF83" s="2" t="inlineStr"/>
+      <c r="AG83" s="2" t="inlineStr"/>
+      <c r="AH83" s="2" t="inlineStr"/>
+      <c r="AI83" s="2" t="inlineStr"/>
+      <c r="AJ83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>f389d37c510f4916</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>67578</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>0.52695</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>-0.07305000000000006</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:38.641492Z</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="W84" s="2" t="inlineStr"/>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr"/>
+      <c r="Z84" s="2" t="inlineStr"/>
+      <c r="AA84" s="2" t="inlineStr"/>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr"/>
+      <c r="AE84" s="2" t="inlineStr"/>
+      <c r="AF84" s="2" t="inlineStr"/>
+      <c r="AG84" s="2" t="inlineStr"/>
+      <c r="AH84" s="2" t="inlineStr"/>
+      <c r="AI84" s="2" t="inlineStr"/>
+      <c r="AJ84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>fb59384cd10b45a9</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>69135</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>0.527213</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>-0.1024166296296295</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:39.222086Z</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr"/>
+      <c r="W85" s="2" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr"/>
+      <c r="Z85" s="2" t="inlineStr"/>
+      <c r="AA85" s="2" t="inlineStr"/>
+      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr"/>
+      <c r="AE85" s="2" t="inlineStr"/>
+      <c r="AF85" s="2" t="inlineStr"/>
+      <c r="AG85" s="2" t="inlineStr"/>
+      <c r="AH85" s="2" t="inlineStr"/>
+      <c r="AI85" s="2" t="inlineStr"/>
+      <c r="AJ85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>c806d81598984a2e</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>67579</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>0.526317</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>0.18618094557823134</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:39.764070Z</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="2" t="inlineStr"/>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr"/>
+      <c r="Z86" s="2" t="inlineStr"/>
+      <c r="AA86" s="2" t="inlineStr"/>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr"/>
+      <c r="AE86" s="2" t="inlineStr"/>
+      <c r="AF86" s="2" t="inlineStr"/>
+      <c r="AG86" s="2" t="inlineStr"/>
+      <c r="AH86" s="2" t="inlineStr"/>
+      <c r="AI86" s="2" t="inlineStr"/>
+      <c r="AJ86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>5f8b3c7825a444e3</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>0.663166</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>0.022878230215827355</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:40.237935Z</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr"/>
+      <c r="W87" s="2" t="inlineStr"/>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr"/>
+      <c r="Z87" s="2" t="inlineStr"/>
+      <c r="AA87" s="2" t="inlineStr"/>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr"/>
+      <c r="AE87" s="2" t="inlineStr"/>
+      <c r="AF87" s="2" t="inlineStr"/>
+      <c r="AG87" s="2" t="inlineStr"/>
+      <c r="AH87" s="2" t="inlineStr"/>
+      <c r="AI87" s="2" t="inlineStr"/>
+      <c r="AJ87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>f7231c54c30e41d0</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>68292</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>0.614</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>-0.026287769784172688</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:40.707211Z</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr"/>
+      <c r="W88" s="2" t="inlineStr"/>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="AA88" s="2" t="inlineStr"/>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr"/>
+      <c r="AE88" s="2" t="inlineStr"/>
+      <c r="AF88" s="2" t="inlineStr"/>
+      <c r="AG88" s="2" t="inlineStr"/>
+      <c r="AH88" s="2" t="inlineStr"/>
+      <c r="AI88" s="2" t="inlineStr"/>
+      <c r="AJ88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>46d6bc7c4b804e4b</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>0.569685</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>0.11923454954954948</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.989547Z</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr"/>
+      <c r="W89" s="2" t="inlineStr"/>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr"/>
+      <c r="Z89" s="2" t="inlineStr"/>
+      <c r="AA89" s="2" t="inlineStr"/>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr"/>
+      <c r="AE89" s="2" t="inlineStr"/>
+      <c r="AF89" s="2" t="inlineStr"/>
+      <c r="AG89" s="2" t="inlineStr"/>
+      <c r="AH89" s="2" t="inlineStr"/>
+      <c r="AI89" s="2" t="inlineStr"/>
+      <c r="AJ89" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ77"/>
+  <autoFilter ref="A1:AJ89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/model_ledgers/cs2-tiered-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$296</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$313</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ296"/>
+  <dimension ref="A1:AJ313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -31638,8 +31638,1742 @@
       <c r="AI296" s="2" t="inlineStr"/>
       <c r="AJ296" s="2" t="inlineStr"/>
     </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>5923ce46bfb647fb</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>79509</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K297" s="2" t="inlineStr"/>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>0.528366</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="inlineStr"/>
+      <c r="N297" s="2" t="inlineStr"/>
+      <c r="O297" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P297" s="2" t="inlineStr"/>
+      <c r="Q297" s="2" t="inlineStr">
+        <is>
+          <t>-0.010804506912442391</t>
+        </is>
+      </c>
+      <c r="R297" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:27.882306Z</t>
+        </is>
+      </c>
+      <c r="S297" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T297" s="2" t="inlineStr"/>
+      <c r="U297" s="2" t="inlineStr"/>
+      <c r="V297" s="2" t="inlineStr"/>
+      <c r="W297" s="2" t="inlineStr"/>
+      <c r="X297" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y297" s="2" t="inlineStr"/>
+      <c r="Z297" s="2" t="inlineStr"/>
+      <c r="AA297" s="2" t="inlineStr"/>
+      <c r="AB297" s="2" t="inlineStr"/>
+      <c r="AC297" s="2" t="inlineStr"/>
+      <c r="AD297" s="2" t="inlineStr"/>
+      <c r="AE297" s="2" t="inlineStr"/>
+      <c r="AF297" s="2" t="inlineStr"/>
+      <c r="AG297" s="2" t="inlineStr"/>
+      <c r="AH297" s="2" t="inlineStr"/>
+      <c r="AI297" s="2" t="inlineStr"/>
+      <c r="AJ297" s="2" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>9d79c87a2b474a9d</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>76994</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J298" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K298" s="2" t="inlineStr"/>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>0.6934</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="inlineStr"/>
+      <c r="N298" s="2" t="inlineStr"/>
+      <c r="O298" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P298" s="2" t="inlineStr"/>
+      <c r="Q298" s="2" t="inlineStr">
+        <is>
+          <t>0.06377037037037048</t>
+        </is>
+      </c>
+      <c r="R298" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:30.180249Z</t>
+        </is>
+      </c>
+      <c r="S298" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:30:00Z</t>
+        </is>
+      </c>
+      <c r="T298" s="2" t="inlineStr"/>
+      <c r="U298" s="2" t="inlineStr"/>
+      <c r="V298" s="2" t="inlineStr"/>
+      <c r="W298" s="2" t="inlineStr"/>
+      <c r="X298" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y298" s="2" t="inlineStr"/>
+      <c r="Z298" s="2" t="inlineStr"/>
+      <c r="AA298" s="2" t="inlineStr"/>
+      <c r="AB298" s="2" t="inlineStr"/>
+      <c r="AC298" s="2" t="inlineStr"/>
+      <c r="AD298" s="2" t="inlineStr"/>
+      <c r="AE298" s="2" t="inlineStr"/>
+      <c r="AF298" s="2" t="inlineStr"/>
+      <c r="AG298" s="2" t="inlineStr"/>
+      <c r="AH298" s="2" t="inlineStr"/>
+      <c r="AI298" s="2" t="inlineStr"/>
+      <c r="AJ298" s="2" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>e6a5159b711e4f32</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>79585</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K299" s="2" t="inlineStr"/>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>0.547765</t>
+        </is>
+      </c>
+      <c r="M299" s="2" t="inlineStr"/>
+      <c r="N299" s="2" t="inlineStr"/>
+      <c r="O299" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P299" s="2" t="inlineStr"/>
+      <c r="Q299" s="2" t="inlineStr">
+        <is>
+          <t>-0.09252276978417273</t>
+        </is>
+      </c>
+      <c r="R299" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:31.590961Z</t>
+        </is>
+      </c>
+      <c r="S299" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T299" s="2" t="inlineStr"/>
+      <c r="U299" s="2" t="inlineStr"/>
+      <c r="V299" s="2" t="inlineStr"/>
+      <c r="W299" s="2" t="inlineStr"/>
+      <c r="X299" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y299" s="2" t="inlineStr"/>
+      <c r="Z299" s="2" t="inlineStr"/>
+      <c r="AA299" s="2" t="inlineStr"/>
+      <c r="AB299" s="2" t="inlineStr"/>
+      <c r="AC299" s="2" t="inlineStr"/>
+      <c r="AD299" s="2" t="inlineStr"/>
+      <c r="AE299" s="2" t="inlineStr"/>
+      <c r="AF299" s="2" t="inlineStr"/>
+      <c r="AG299" s="2" t="inlineStr"/>
+      <c r="AH299" s="2" t="inlineStr"/>
+      <c r="AI299" s="2" t="inlineStr"/>
+      <c r="AJ299" s="2" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>5643fd7c97d1439d</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>79586</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J300" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K300" s="2" t="inlineStr"/>
+      <c r="L300" s="2" t="inlineStr">
+        <is>
+          <t>0.520239</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="inlineStr"/>
+      <c r="N300" s="2" t="inlineStr"/>
+      <c r="O300" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P300" s="2" t="inlineStr"/>
+      <c r="Q300" s="2" t="inlineStr">
+        <is>
+          <t>0.16052676978417268</t>
+        </is>
+      </c>
+      <c r="R300" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:32.440016Z</t>
+        </is>
+      </c>
+      <c r="S300" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T300" s="2" t="inlineStr"/>
+      <c r="U300" s="2" t="inlineStr"/>
+      <c r="V300" s="2" t="inlineStr"/>
+      <c r="W300" s="2" t="inlineStr"/>
+      <c r="X300" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y300" s="2" t="inlineStr"/>
+      <c r="Z300" s="2" t="inlineStr"/>
+      <c r="AA300" s="2" t="inlineStr"/>
+      <c r="AB300" s="2" t="inlineStr"/>
+      <c r="AC300" s="2" t="inlineStr"/>
+      <c r="AD300" s="2" t="inlineStr"/>
+      <c r="AE300" s="2" t="inlineStr"/>
+      <c r="AF300" s="2" t="inlineStr"/>
+      <c r="AG300" s="2" t="inlineStr"/>
+      <c r="AH300" s="2" t="inlineStr"/>
+      <c r="AI300" s="2" t="inlineStr"/>
+      <c r="AJ300" s="2" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>215e60e13ea74414</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>79587</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J301" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K301" s="2" t="inlineStr"/>
+      <c r="L301" s="2" t="inlineStr">
+        <is>
+          <t>0.507097</t>
+        </is>
+      </c>
+      <c r="M301" s="2" t="inlineStr"/>
+      <c r="N301" s="2" t="inlineStr"/>
+      <c r="O301" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P301" s="2" t="inlineStr"/>
+      <c r="Q301" s="2" t="inlineStr">
+        <is>
+          <t>-0.05237436563876652</t>
+        </is>
+      </c>
+      <c r="R301" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:33.140301Z</t>
+        </is>
+      </c>
+      <c r="S301" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T23:45:00Z</t>
+        </is>
+      </c>
+      <c r="T301" s="2" t="inlineStr"/>
+      <c r="U301" s="2" t="inlineStr"/>
+      <c r="V301" s="2" t="inlineStr"/>
+      <c r="W301" s="2" t="inlineStr"/>
+      <c r="X301" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y301" s="2" t="inlineStr"/>
+      <c r="Z301" s="2" t="inlineStr"/>
+      <c r="AA301" s="2" t="inlineStr"/>
+      <c r="AB301" s="2" t="inlineStr"/>
+      <c r="AC301" s="2" t="inlineStr"/>
+      <c r="AD301" s="2" t="inlineStr"/>
+      <c r="AE301" s="2" t="inlineStr"/>
+      <c r="AF301" s="2" t="inlineStr"/>
+      <c r="AG301" s="2" t="inlineStr"/>
+      <c r="AH301" s="2" t="inlineStr"/>
+      <c r="AI301" s="2" t="inlineStr"/>
+      <c r="AJ301" s="2" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>6237643e659a4063</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>78271</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K302" s="2" t="inlineStr"/>
+      <c r="L302" s="2" t="inlineStr">
+        <is>
+          <t>0.657895</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="inlineStr"/>
+      <c r="N302" s="2" t="inlineStr"/>
+      <c r="O302" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P302" s="2" t="inlineStr"/>
+      <c r="Q302" s="2" t="inlineStr">
+        <is>
+          <t>0.0075453496503496975</t>
+        </is>
+      </c>
+      <c r="R302" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:34.428376Z</t>
+        </is>
+      </c>
+      <c r="S302" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T302" s="2" t="inlineStr"/>
+      <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" s="2" t="inlineStr"/>
+      <c r="W302" s="2" t="inlineStr"/>
+      <c r="X302" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y302" s="2" t="inlineStr"/>
+      <c r="Z302" s="2" t="inlineStr"/>
+      <c r="AA302" s="2" t="inlineStr"/>
+      <c r="AB302" s="2" t="inlineStr"/>
+      <c r="AC302" s="2" t="inlineStr"/>
+      <c r="AD302" s="2" t="inlineStr"/>
+      <c r="AE302" s="2" t="inlineStr"/>
+      <c r="AF302" s="2" t="inlineStr"/>
+      <c r="AG302" s="2" t="inlineStr"/>
+      <c r="AH302" s="2" t="inlineStr"/>
+      <c r="AI302" s="2" t="inlineStr"/>
+      <c r="AJ302" s="2" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>aa0d2664e562473e</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>78269</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K303" s="2" t="inlineStr"/>
+      <c r="L303" s="2" t="inlineStr">
+        <is>
+          <t>0.718387</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="inlineStr"/>
+      <c r="N303" s="2" t="inlineStr"/>
+      <c r="O303" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P303" s="2" t="inlineStr"/>
+      <c r="Q303" s="2" t="inlineStr">
+        <is>
+          <t>0.018687300300300302</t>
+        </is>
+      </c>
+      <c r="R303" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:35.148843Z</t>
+        </is>
+      </c>
+      <c r="S303" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T303" s="2" t="inlineStr"/>
+      <c r="U303" s="2" t="inlineStr"/>
+      <c r="V303" s="2" t="inlineStr"/>
+      <c r="W303" s="2" t="inlineStr"/>
+      <c r="X303" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y303" s="2" t="inlineStr"/>
+      <c r="Z303" s="2" t="inlineStr"/>
+      <c r="AA303" s="2" t="inlineStr"/>
+      <c r="AB303" s="2" t="inlineStr"/>
+      <c r="AC303" s="2" t="inlineStr"/>
+      <c r="AD303" s="2" t="inlineStr"/>
+      <c r="AE303" s="2" t="inlineStr"/>
+      <c r="AF303" s="2" t="inlineStr"/>
+      <c r="AG303" s="2" t="inlineStr"/>
+      <c r="AH303" s="2" t="inlineStr"/>
+      <c r="AI303" s="2" t="inlineStr"/>
+      <c r="AJ303" s="2" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>9fb9c0cac9ad4b02</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>79634</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K304" s="2" t="inlineStr"/>
+      <c r="L304" s="2" t="inlineStr">
+        <is>
+          <t>0.595884</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="inlineStr"/>
+      <c r="N304" s="2" t="inlineStr"/>
+      <c r="O304" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P304" s="2" t="inlineStr"/>
+      <c r="Q304" s="2" t="inlineStr">
+        <is>
+          <t>-0.06397994557823139</t>
+        </is>
+      </c>
+      <c r="R304" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:36.802526Z</t>
+        </is>
+      </c>
+      <c r="S304" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T304" s="2" t="inlineStr"/>
+      <c r="U304" s="2" t="inlineStr"/>
+      <c r="V304" s="2" t="inlineStr"/>
+      <c r="W304" s="2" t="inlineStr"/>
+      <c r="X304" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y304" s="2" t="inlineStr"/>
+      <c r="Z304" s="2" t="inlineStr"/>
+      <c r="AA304" s="2" t="inlineStr"/>
+      <c r="AB304" s="2" t="inlineStr"/>
+      <c r="AC304" s="2" t="inlineStr"/>
+      <c r="AD304" s="2" t="inlineStr"/>
+      <c r="AE304" s="2" t="inlineStr"/>
+      <c r="AF304" s="2" t="inlineStr"/>
+      <c r="AG304" s="2" t="inlineStr"/>
+      <c r="AH304" s="2" t="inlineStr"/>
+      <c r="AI304" s="2" t="inlineStr"/>
+      <c r="AJ304" s="2" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>220e9c72a5b74526</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>79649</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K305" s="2" t="inlineStr"/>
+      <c r="L305" s="2" t="inlineStr">
+        <is>
+          <t>0.535279</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="inlineStr"/>
+      <c r="N305" s="2" t="inlineStr"/>
+      <c r="O305" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P305" s="2" t="inlineStr"/>
+      <c r="Q305" s="2" t="inlineStr">
+        <is>
+          <t>-0.10500876978417273</t>
+        </is>
+      </c>
+      <c r="R305" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:38.290660Z</t>
+        </is>
+      </c>
+      <c r="S305" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T305" s="2" t="inlineStr"/>
+      <c r="U305" s="2" t="inlineStr"/>
+      <c r="V305" s="2" t="inlineStr"/>
+      <c r="W305" s="2" t="inlineStr"/>
+      <c r="X305" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y305" s="2" t="inlineStr"/>
+      <c r="Z305" s="2" t="inlineStr"/>
+      <c r="AA305" s="2" t="inlineStr"/>
+      <c r="AB305" s="2" t="inlineStr"/>
+      <c r="AC305" s="2" t="inlineStr"/>
+      <c r="AD305" s="2" t="inlineStr"/>
+      <c r="AE305" s="2" t="inlineStr"/>
+      <c r="AF305" s="2" t="inlineStr"/>
+      <c r="AG305" s="2" t="inlineStr"/>
+      <c r="AH305" s="2" t="inlineStr"/>
+      <c r="AI305" s="2" t="inlineStr"/>
+      <c r="AJ305" s="2" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>096f785ffcad464f</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>79631</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K306" s="2" t="inlineStr"/>
+      <c r="L306" s="2" t="inlineStr">
+        <is>
+          <t>0.508187</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="inlineStr"/>
+      <c r="N306" s="2" t="inlineStr"/>
+      <c r="O306" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P306" s="2" t="inlineStr"/>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>0.15853665034965042</t>
+        </is>
+      </c>
+      <c r="R306" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:39.114673Z</t>
+        </is>
+      </c>
+      <c r="S306" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T306" s="2" t="inlineStr"/>
+      <c r="U306" s="2" t="inlineStr"/>
+      <c r="V306" s="2" t="inlineStr"/>
+      <c r="W306" s="2" t="inlineStr"/>
+      <c r="X306" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y306" s="2" t="inlineStr"/>
+      <c r="Z306" s="2" t="inlineStr"/>
+      <c r="AA306" s="2" t="inlineStr"/>
+      <c r="AB306" s="2" t="inlineStr"/>
+      <c r="AC306" s="2" t="inlineStr"/>
+      <c r="AD306" s="2" t="inlineStr"/>
+      <c r="AE306" s="2" t="inlineStr"/>
+      <c r="AF306" s="2" t="inlineStr"/>
+      <c r="AG306" s="2" t="inlineStr"/>
+      <c r="AH306" s="2" t="inlineStr"/>
+      <c r="AI306" s="2" t="inlineStr"/>
+      <c r="AJ306" s="2" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>501755a64a274eaf</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>78272</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K307" s="2" t="inlineStr"/>
+      <c r="L307" s="2" t="inlineStr">
+        <is>
+          <t>0.602048</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="inlineStr"/>
+      <c r="N307" s="2" t="inlineStr"/>
+      <c r="O307" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P307" s="2" t="inlineStr"/>
+      <c r="Q307" s="2" t="inlineStr">
+        <is>
+          <t>0.08281723076923087</t>
+        </is>
+      </c>
+      <c r="R307" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:39.722924Z</t>
+        </is>
+      </c>
+      <c r="S307" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T307" s="2" t="inlineStr"/>
+      <c r="U307" s="2" t="inlineStr"/>
+      <c r="V307" s="2" t="inlineStr"/>
+      <c r="W307" s="2" t="inlineStr"/>
+      <c r="X307" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y307" s="2" t="inlineStr"/>
+      <c r="Z307" s="2" t="inlineStr"/>
+      <c r="AA307" s="2" t="inlineStr"/>
+      <c r="AB307" s="2" t="inlineStr"/>
+      <c r="AC307" s="2" t="inlineStr"/>
+      <c r="AD307" s="2" t="inlineStr"/>
+      <c r="AE307" s="2" t="inlineStr"/>
+      <c r="AF307" s="2" t="inlineStr"/>
+      <c r="AG307" s="2" t="inlineStr"/>
+      <c r="AH307" s="2" t="inlineStr"/>
+      <c r="AI307" s="2" t="inlineStr"/>
+      <c r="AJ307" s="2" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>29d04b2b941b45e9</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>78273</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K308" s="2" t="inlineStr"/>
+      <c r="L308" s="2" t="inlineStr">
+        <is>
+          <t>0.542742</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="inlineStr"/>
+      <c r="N308" s="2" t="inlineStr"/>
+      <c r="O308" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P308" s="2" t="inlineStr"/>
+      <c r="Q308" s="2" t="inlineStr">
+        <is>
+          <t>-0.04742193442622955</t>
+        </is>
+      </c>
+      <c r="R308" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:41.523712Z</t>
+        </is>
+      </c>
+      <c r="S308" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T308" s="2" t="inlineStr"/>
+      <c r="U308" s="2" t="inlineStr"/>
+      <c r="V308" s="2" t="inlineStr"/>
+      <c r="W308" s="2" t="inlineStr"/>
+      <c r="X308" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y308" s="2" t="inlineStr"/>
+      <c r="Z308" s="2" t="inlineStr"/>
+      <c r="AA308" s="2" t="inlineStr"/>
+      <c r="AB308" s="2" t="inlineStr"/>
+      <c r="AC308" s="2" t="inlineStr"/>
+      <c r="AD308" s="2" t="inlineStr"/>
+      <c r="AE308" s="2" t="inlineStr"/>
+      <c r="AF308" s="2" t="inlineStr"/>
+      <c r="AG308" s="2" t="inlineStr"/>
+      <c r="AH308" s="2" t="inlineStr"/>
+      <c r="AI308" s="2" t="inlineStr"/>
+      <c r="AJ308" s="2" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>6f28688981964602</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>79708</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K309" s="2" t="inlineStr"/>
+      <c r="L309" s="2" t="inlineStr">
+        <is>
+          <t>0.578141</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="inlineStr"/>
+      <c r="N309" s="2" t="inlineStr"/>
+      <c r="O309" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P309" s="2" t="inlineStr"/>
+      <c r="Q309" s="2" t="inlineStr">
+        <is>
+          <t>0.14895645064377683</t>
+        </is>
+      </c>
+      <c r="R309" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:42.889383Z</t>
+        </is>
+      </c>
+      <c r="S309" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T309" s="2" t="inlineStr"/>
+      <c r="U309" s="2" t="inlineStr"/>
+      <c r="V309" s="2" t="inlineStr"/>
+      <c r="W309" s="2" t="inlineStr"/>
+      <c r="X309" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y309" s="2" t="inlineStr"/>
+      <c r="Z309" s="2" t="inlineStr"/>
+      <c r="AA309" s="2" t="inlineStr"/>
+      <c r="AB309" s="2" t="inlineStr"/>
+      <c r="AC309" s="2" t="inlineStr"/>
+      <c r="AD309" s="2" t="inlineStr"/>
+      <c r="AE309" s="2" t="inlineStr"/>
+      <c r="AF309" s="2" t="inlineStr"/>
+      <c r="AG309" s="2" t="inlineStr"/>
+      <c r="AH309" s="2" t="inlineStr"/>
+      <c r="AI309" s="2" t="inlineStr"/>
+      <c r="AJ309" s="2" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>04450c98267347de</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>78274</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K310" s="2" t="inlineStr"/>
+      <c r="L310" s="2" t="inlineStr">
+        <is>
+          <t>0.514649</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="inlineStr"/>
+      <c r="N310" s="2" t="inlineStr"/>
+      <c r="O310" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P310" s="2" t="inlineStr"/>
+      <c r="Q310" s="2" t="inlineStr">
+        <is>
+          <t>-0.06518293277310916</t>
+        </is>
+      </c>
+      <c r="R310" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:45.169244Z</t>
+        </is>
+      </c>
+      <c r="S310" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T310" s="2" t="inlineStr"/>
+      <c r="U310" s="2" t="inlineStr"/>
+      <c r="V310" s="2" t="inlineStr"/>
+      <c r="W310" s="2" t="inlineStr"/>
+      <c r="X310" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y310" s="2" t="inlineStr"/>
+      <c r="Z310" s="2" t="inlineStr"/>
+      <c r="AA310" s="2" t="inlineStr"/>
+      <c r="AB310" s="2" t="inlineStr"/>
+      <c r="AC310" s="2" t="inlineStr"/>
+      <c r="AD310" s="2" t="inlineStr"/>
+      <c r="AE310" s="2" t="inlineStr"/>
+      <c r="AF310" s="2" t="inlineStr"/>
+      <c r="AG310" s="2" t="inlineStr"/>
+      <c r="AH310" s="2" t="inlineStr"/>
+      <c r="AI310" s="2" t="inlineStr"/>
+      <c r="AJ310" s="2" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>33dbb1aa01dd4351</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>79752</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K311" s="2" t="inlineStr"/>
+      <c r="L311" s="2" t="inlineStr">
+        <is>
+          <t>0.566025</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="inlineStr"/>
+      <c r="N311" s="2" t="inlineStr"/>
+      <c r="O311" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P311" s="2" t="inlineStr"/>
+      <c r="Q311" s="2" t="inlineStr">
+        <is>
+          <t>0.09654143192488263</t>
+        </is>
+      </c>
+      <c r="R311" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:46.085822Z</t>
+        </is>
+      </c>
+      <c r="S311" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T311" s="2" t="inlineStr"/>
+      <c r="U311" s="2" t="inlineStr"/>
+      <c r="V311" s="2" t="inlineStr"/>
+      <c r="W311" s="2" t="inlineStr"/>
+      <c r="X311" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y311" s="2" t="inlineStr"/>
+      <c r="Z311" s="2" t="inlineStr"/>
+      <c r="AA311" s="2" t="inlineStr"/>
+      <c r="AB311" s="2" t="inlineStr"/>
+      <c r="AC311" s="2" t="inlineStr"/>
+      <c r="AD311" s="2" t="inlineStr"/>
+      <c r="AE311" s="2" t="inlineStr"/>
+      <c r="AF311" s="2" t="inlineStr"/>
+      <c r="AG311" s="2" t="inlineStr"/>
+      <c r="AH311" s="2" t="inlineStr"/>
+      <c r="AI311" s="2" t="inlineStr"/>
+      <c r="AJ311" s="2" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>3d699c982ea345dd</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>78152</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K312" s="2" t="inlineStr"/>
+      <c r="L312" s="2" t="inlineStr">
+        <is>
+          <t>0.525473</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="inlineStr"/>
+      <c r="N312" s="2" t="inlineStr"/>
+      <c r="O312" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P312" s="2" t="inlineStr"/>
+      <c r="Q312" s="2" t="inlineStr">
+        <is>
+          <t>0.04470376923076924</t>
+        </is>
+      </c>
+      <c r="R312" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:46.944846Z</t>
+        </is>
+      </c>
+      <c r="S312" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T312" s="2" t="inlineStr"/>
+      <c r="U312" s="2" t="inlineStr"/>
+      <c r="V312" s="2" t="inlineStr"/>
+      <c r="W312" s="2" t="inlineStr"/>
+      <c r="X312" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y312" s="2" t="inlineStr"/>
+      <c r="Z312" s="2" t="inlineStr"/>
+      <c r="AA312" s="2" t="inlineStr"/>
+      <c r="AB312" s="2" t="inlineStr"/>
+      <c r="AC312" s="2" t="inlineStr"/>
+      <c r="AD312" s="2" t="inlineStr"/>
+      <c r="AE312" s="2" t="inlineStr"/>
+      <c r="AF312" s="2" t="inlineStr"/>
+      <c r="AG312" s="2" t="inlineStr"/>
+      <c r="AH312" s="2" t="inlineStr"/>
+      <c r="AI312" s="2" t="inlineStr"/>
+      <c r="AJ312" s="2" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>34914b3f53b74f23</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>79589</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K313" s="2" t="inlineStr"/>
+      <c r="L313" s="2" t="inlineStr">
+        <is>
+          <t>0.556804</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="inlineStr"/>
+      <c r="N313" s="2" t="inlineStr"/>
+      <c r="O313" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P313" s="2" t="inlineStr"/>
+      <c r="Q313" s="2" t="inlineStr">
+        <is>
+          <t>-0.12370718210862619</t>
+        </is>
+      </c>
+      <c r="R313" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:50.524295Z</t>
+        </is>
+      </c>
+      <c r="S313" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T23:45:00Z</t>
+        </is>
+      </c>
+      <c r="T313" s="2" t="inlineStr"/>
+      <c r="U313" s="2" t="inlineStr"/>
+      <c r="V313" s="2" t="inlineStr"/>
+      <c r="W313" s="2" t="inlineStr"/>
+      <c r="X313" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y313" s="2" t="inlineStr"/>
+      <c r="Z313" s="2" t="inlineStr"/>
+      <c r="AA313" s="2" t="inlineStr"/>
+      <c r="AB313" s="2" t="inlineStr"/>
+      <c r="AC313" s="2" t="inlineStr"/>
+      <c r="AD313" s="2" t="inlineStr"/>
+      <c r="AE313" s="2" t="inlineStr"/>
+      <c r="AF313" s="2" t="inlineStr"/>
+      <c r="AG313" s="2" t="inlineStr"/>
+      <c r="AH313" s="2" t="inlineStr"/>
+      <c r="AI313" s="2" t="inlineStr"/>
+      <c r="AJ313" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ296"/>
+  <autoFilter ref="A1:AJ313"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$314</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ313"/>
+  <dimension ref="A1:AJ314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -33372,8 +33372,110 @@
       <c r="AI313" s="2" t="inlineStr"/>
       <c r="AJ313" s="2" t="inlineStr"/>
     </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>bc1583948fdf42e4</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>79707</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K314" s="2" t="inlineStr"/>
+      <c r="L314" s="2" t="inlineStr">
+        <is>
+          <t>0.589871</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="inlineStr"/>
+      <c r="N314" s="2" t="inlineStr"/>
+      <c r="O314" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P314" s="2" t="inlineStr"/>
+      <c r="Q314" s="2" t="inlineStr">
+        <is>
+          <t>0.030399634361233496</t>
+        </is>
+      </c>
+      <c r="R314" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:34:12.073189Z</t>
+        </is>
+      </c>
+      <c r="S314" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T314" s="2" t="inlineStr"/>
+      <c r="U314" s="2" t="inlineStr"/>
+      <c r="V314" s="2" t="inlineStr"/>
+      <c r="W314" s="2" t="inlineStr"/>
+      <c r="X314" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y314" s="2" t="inlineStr"/>
+      <c r="Z314" s="2" t="inlineStr"/>
+      <c r="AA314" s="2" t="inlineStr"/>
+      <c r="AB314" s="2" t="inlineStr"/>
+      <c r="AC314" s="2" t="inlineStr"/>
+      <c r="AD314" s="2" t="inlineStr"/>
+      <c r="AE314" s="2" t="inlineStr"/>
+      <c r="AF314" s="2" t="inlineStr"/>
+      <c r="AG314" s="2" t="inlineStr"/>
+      <c r="AH314" s="2" t="inlineStr"/>
+      <c r="AI314" s="2" t="inlineStr"/>
+      <c r="AJ314" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ313"/>
+  <autoFilter ref="A1:AJ314"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>